--- a/Wyniki/next pull.xlsx
+++ b/Wyniki/next pull.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\RackIT\Wyniki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61C2A18-972E-481D-A748-EE651F92EEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A597633-BE91-40BD-8697-55BC2F8E715D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUSH – Klatka · Barki · Triceps" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="159">
   <si>
     <t>PUSH – Klatka · Barki · Triceps</t>
   </si>
@@ -367,9 +367,6 @@
     <t>RIR 1  –  7 powt., 1 w zapasie</t>
   </si>
   <si>
-    <t>nachwyt / podchwyt naprzemiennie co sesję</t>
-  </si>
-  <si>
     <t>Uginanie hantlami stojąc</t>
   </si>
   <si>
@@ -511,10 +508,16 @@
     <t xml:space="preserve"> 8-10</t>
   </si>
   <si>
-    <t>2 x 10</t>
-  </si>
-  <si>
     <t>2 x 12,5</t>
+  </si>
+  <si>
+    <t>RIR 1  –  9-10 powt., 1 w zapasie</t>
+  </si>
+  <si>
+    <t>RIR 2  –  8-9 powt., 2 w zapasie</t>
+  </si>
+  <si>
+    <t>neutral</t>
   </si>
 </sst>
 </file>
@@ -996,6 +999,9 @@
     <xf numFmtId="0" fontId="26" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1058,55 +1064,53 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1120,46 +1124,45 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1490,78 +1493,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
     </row>
     <row r="3" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
     </row>
     <row r="6" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1570,26 +1573,26 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="79" t="s">
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="79" t="s">
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="79" t="s">
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="80"/>
-      <c r="R6" s="80"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
@@ -1885,111 +1888,111 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="66"/>
-      <c r="M13" s="66"/>
-      <c r="N13" s="66"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="67"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
     </row>
     <row r="15" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
     </row>
     <row r="16" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="84"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="83" t="s">
+      <c r="G16" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="84"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="84"/>
-      <c r="P16" s="84"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="84"/>
-      <c r="S16" s="84"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="87"/>
+      <c r="O16" s="87"/>
+      <c r="P16" s="87"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="87"/>
+      <c r="S16" s="87"/>
       <c r="T16" s="21"/>
     </row>
     <row r="17" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
       <c r="F17" s="24" t="s">
         <v>9</v>
       </c>
       <c r="G17" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="86"/>
-      <c r="M17" s="86"/>
-      <c r="N17" s="86"/>
-      <c r="O17" s="86"/>
-      <c r="P17" s="86"/>
-      <c r="Q17" s="86"/>
-      <c r="R17" s="86"/>
-      <c r="S17" s="86"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="78"/>
       <c r="T17" s="23"/>
     </row>
     <row r="18" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2005,7 +2008,7 @@
       <c r="F18" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="62" t="s">
+      <c r="G18" s="70" t="s">
         <v>13</v>
       </c>
       <c r="H18" s="61"/>
@@ -2026,30 +2029,30 @@
       <c r="A19" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
       <c r="F19" s="24" t="s">
         <v>16</v>
       </c>
       <c r="G19" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="86"/>
-      <c r="O19" s="86"/>
-      <c r="P19" s="86"/>
-      <c r="Q19" s="86"/>
-      <c r="R19" s="86"/>
-      <c r="S19" s="86"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="78"/>
       <c r="T19" s="23"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2065,7 +2068,7 @@
       <c r="F20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="62" t="s">
+      <c r="G20" s="70" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="61"/>
@@ -2086,72 +2089,73 @@
       <c r="A21" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
       <c r="F21" s="24" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="86"/>
-      <c r="I21" s="86"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="86"/>
-      <c r="L21" s="86"/>
-      <c r="M21" s="86"/>
-      <c r="N21" s="86"/>
-      <c r="O21" s="86"/>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="86"/>
-      <c r="R21" s="86"/>
-      <c r="S21" s="86"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="78"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
+      <c r="Q21" s="78"/>
+      <c r="R21" s="78"/>
+      <c r="S21" s="78"/>
       <c r="T21" s="23"/>
     </row>
     <row r="22" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A22:T22"/>
-    <mergeCell ref="G16:S16"/>
-    <mergeCell ref="G19:S19"/>
-    <mergeCell ref="G18:S18"/>
-    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="G21:S21"/>
+    <mergeCell ref="B20:E20"/>
     <mergeCell ref="G17:S17"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="G21:S21"/>
+    <mergeCell ref="G19:S19"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="G16:S16"/>
+    <mergeCell ref="G20:S20"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="G18:S18"/>
     <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="G20:S20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="A13:T13"/>
+    <mergeCell ref="B19:E19"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="M6:O6"/>
@@ -2159,7 +2163,6 @@
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="A5:T5"/>
     <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A13:T13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -2195,78 +2198,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
     </row>
     <row r="3" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
     </row>
     <row r="6" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28"/>
@@ -2275,30 +2278,30 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="67" t="s">
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="67" t="s">
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="67" t="s">
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="63"/>
       <c r="S6" s="28"/>
       <c r="T6" s="28"/>
     </row>
-    <row r="7" spans="1:20" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="38.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>29</v>
       </c>
@@ -2360,7 +2363,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="30">
         <v>1</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>98</v>
       </c>
       <c r="E8" s="33">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="F8" s="34" t="s">
         <v>99</v>
@@ -2413,7 +2416,7 @@
       </c>
       <c r="T8" s="35"/>
     </row>
-    <row r="9" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2</v>
       </c>
@@ -2465,51 +2468,51 @@
         <v>–</v>
       </c>
       <c r="T9" s="18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30">
         <v>3</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" s="32">
         <v>4</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E10" s="33">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G10" s="32">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="9" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="J10" s="32">
-        <v>60</v>
-      </c>
-      <c r="K10" s="59"/>
+        <v>62.5</v>
+      </c>
+      <c r="K10" s="37"/>
       <c r="L10" s="10" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="M10" s="32">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="N10" s="32"/>
       <c r="O10" s="10" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="P10" s="32">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="Q10" s="32"/>
       <c r="R10" s="11" t="s">
@@ -2521,41 +2524,41 @@
       </c>
       <c r="T10" s="35"/>
     </row>
-    <row r="11" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>4</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="10" t="s">
         <v>69</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="11" t="s">
@@ -2568,60 +2571,60 @@
         <f>IF(N11="","–",IF(ISNUMBER(N11),IF(N11&gt;12,"✓ TAK – dodaj 2,5 kg","✗ NIE – zostań z ciężarem"),"–"))</f>
         <v>–</v>
       </c>
-      <c r="T11" s="37" t="s">
-        <v>111</v>
+      <c r="T11" s="38" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="66"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
     </row>
     <row r="14" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="66"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="66"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="67"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
     </row>
     <row r="15" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="39" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="73" t="s">
@@ -2630,7 +2633,7 @@
       <c r="C15" s="74"/>
       <c r="D15" s="74"/>
       <c r="E15" s="74"/>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="39" t="s">
         <v>5</v>
       </c>
       <c r="G15" s="73" t="s">
@@ -2648,37 +2651,37 @@
       <c r="Q15" s="74"/>
       <c r="R15" s="74"/>
       <c r="S15" s="74"/>
-      <c r="T15" s="39"/>
+      <c r="T15" s="40"/>
     </row>
     <row r="16" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="70" t="s">
+      <c r="B16" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="42" t="s">
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="63" t="s">
+      <c r="G16" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="64"/>
-      <c r="O16" s="64"/>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="64"/>
-      <c r="R16" s="64"/>
-      <c r="S16" s="64"/>
-      <c r="T16" s="41"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="65"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="42"/>
     </row>
     <row r="17" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
@@ -2690,10 +2693,10 @@
       <c r="C17" s="61"/>
       <c r="D17" s="61"/>
       <c r="E17" s="61"/>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="62" t="s">
+      <c r="G17" s="70" t="s">
         <v>77</v>
       </c>
       <c r="H17" s="61"/>
@@ -2711,34 +2714,34 @@
       <c r="T17" s="26"/>
     </row>
     <row r="18" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="42" t="s">
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="63" t="s">
+      <c r="G18" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="64"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="64"/>
-      <c r="R18" s="64"/>
-      <c r="S18" s="64"/>
-      <c r="T18" s="41"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="65"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="42"/>
     </row>
     <row r="19" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
@@ -2750,10 +2753,10 @@
       <c r="C19" s="61"/>
       <c r="D19" s="61"/>
       <c r="E19" s="61"/>
-      <c r="F19" s="43" t="s">
+      <c r="F19" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="62" t="s">
+      <c r="G19" s="70" t="s">
         <v>82</v>
       </c>
       <c r="H19" s="61"/>
@@ -2771,34 +2774,34 @@
       <c r="T19" s="26"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="42" t="s">
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="63" t="s">
+      <c r="G20" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="64"/>
-      <c r="R20" s="64"/>
-      <c r="S20" s="64"/>
-      <c r="T20" s="41"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="65"/>
+      <c r="P20" s="65"/>
+      <c r="Q20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65"/>
+      <c r="T20" s="42"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
@@ -2810,10 +2813,10 @@
       <c r="C21" s="61"/>
       <c r="D21" s="61"/>
       <c r="E21" s="61"/>
-      <c r="F21" s="43" t="s">
+      <c r="F21" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="62" t="s">
+      <c r="G21" s="70" t="s">
         <v>86</v>
       </c>
       <c r="H21" s="61"/>
@@ -2831,34 +2834,34 @@
       <c r="T21" s="26"/>
     </row>
     <row r="22" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="42" t="s">
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="63" t="s">
+      <c r="G22" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="64"/>
-      <c r="R22" s="64"/>
-      <c r="S22" s="64"/>
-      <c r="T22" s="41"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="42"/>
     </row>
     <row r="23" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
@@ -2870,10 +2873,10 @@
       <c r="C23" s="61"/>
       <c r="D23" s="61"/>
       <c r="E23" s="61"/>
-      <c r="F23" s="43" t="s">
+      <c r="F23" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="62" t="s">
+      <c r="G23" s="70" t="s">
         <v>90</v>
       </c>
       <c r="H23" s="61"/>
@@ -2891,34 +2894,34 @@
       <c r="T23" s="26"/>
     </row>
     <row r="24" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="42" t="s">
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="63" t="s">
+      <c r="G24" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="64"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="64"/>
-      <c r="R24" s="64"/>
-      <c r="S24" s="64"/>
-      <c r="T24" s="41"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="65"/>
+      <c r="P24" s="65"/>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="42"/>
     </row>
     <row r="25" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
@@ -2930,10 +2933,10 @@
       <c r="C25" s="61"/>
       <c r="D25" s="61"/>
       <c r="E25" s="61"/>
-      <c r="F25" s="43" t="s">
+      <c r="F25" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="70" t="s">
         <v>95</v>
       </c>
       <c r="H25" s="61"/>
@@ -2951,63 +2954,63 @@
       <c r="T25" s="26"/>
     </row>
     <row r="26" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="66"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="32">
     <mergeCell ref="A26:T26"/>
-    <mergeCell ref="G17:S17"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="G23:S23"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="G25:S25"/>
     <mergeCell ref="M6:O6"/>
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="A5:T5"/>
+    <mergeCell ref="G20:S20"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="G18:S18"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="G16:S16"/>
+    <mergeCell ref="G22:S22"/>
+    <mergeCell ref="A14:T14"/>
+    <mergeCell ref="A12:T12"/>
+    <mergeCell ref="G24:S24"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="G19:S19"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
     <mergeCell ref="G15:S15"/>
     <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G17:S17"/>
     <mergeCell ref="G21:S21"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="G18:S18"/>
-    <mergeCell ref="G24:S24"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="G16:S16"/>
-    <mergeCell ref="A14:T14"/>
-    <mergeCell ref="A12:T12"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="G19:S19"/>
-    <mergeCell ref="G22:S22"/>
-    <mergeCell ref="G20:S20"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="G25:S25"/>
-    <mergeCell ref="G23:S23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -3043,222 +3046,222 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
+      <c r="A1" s="92" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
     </row>
     <row r="3" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
     </row>
     <row r="6" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="95" t="s">
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="96"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="95" t="s">
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="95" t="s">
+      <c r="K6" s="95"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="95" t="s">
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="96"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
+      <c r="Q6" s="95"/>
+      <c r="R6" s="95"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="45"/>
     </row>
     <row r="7" spans="1:20" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="45" t="s">
+      <c r="E7" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="45" t="s">
+      <c r="I7" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="45" t="s">
+      <c r="J7" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="45" t="s">
+      <c r="K7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="45" t="s">
+      <c r="L7" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="45" t="s">
+      <c r="M7" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="N7" s="45" t="s">
+      <c r="N7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="45" t="s">
+      <c r="O7" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="45" t="s">
+      <c r="P7" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="Q7" s="45" t="s">
+      <c r="Q7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R7" s="45" t="s">
+      <c r="R7" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="S7" s="45" t="s">
+      <c r="S7" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="T7" s="45" t="s">
+      <c r="T7" s="46" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46">
+      <c r="A8" s="47">
         <v>1</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="49">
+        <v>4</v>
+      </c>
+      <c r="D8" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="48">
-        <v>4</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" s="49">
+      <c r="E8" s="50">
         <v>70</v>
       </c>
       <c r="F8" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
       <c r="I8" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
+        <v>145</v>
+      </c>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
       <c r="L8" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
       <c r="O8" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
       <c r="R8" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="S8" s="48" t="str">
+        <v>146</v>
+      </c>
+      <c r="S8" s="49" t="str">
         <f>IF(Q8="","–",IF(ISNUMBER(Q8),IF(Q8&gt;8,"✓ TAK – dodaj 2,5 kg","✗ NIE – zostań z ciężarem"),"–"))</f>
         <v>–</v>
       </c>
-      <c r="T8" s="50"/>
+      <c r="T8" s="51"/>
     </row>
     <row r="9" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="51">
+      <c r="A9" s="52">
         <v>2</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C9" s="15">
         <v>3</v>
@@ -3275,12 +3278,12 @@
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
       <c r="I9" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
       <c r="L9" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
@@ -3295,177 +3298,177 @@
         <v>–</v>
       </c>
       <c r="T9" s="18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="47">
+        <v>3</v>
+      </c>
+      <c r="B10" s="48" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46">
+      <c r="C10" s="49">
         <v>3</v>
       </c>
-      <c r="B10" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="48">
-        <v>3</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="49">
+      <c r="D10" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="50">
         <v>50</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
       <c r="I10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
       <c r="L10" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
       <c r="O10" s="11" t="s">
         <v>46</v>
       </c>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
-      <c r="S10" s="48" t="str">
+      <c r="S10" s="49" t="str">
         <f>IF(N10="","–",IF(ISNUMBER(N10),IF(N10&gt;12,"✓ TAK – dodaj 2,5 kg","✗ NIE – zostań z ciężarem"),"–"))</f>
         <v>–</v>
       </c>
-      <c r="T10" s="52" t="s">
-        <v>153</v>
+      <c r="T10" s="53" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="66"/>
-      <c r="O11" s="66"/>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="66"/>
-      <c r="R11" s="66"/>
-      <c r="S11" s="66"/>
-      <c r="T11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
     </row>
     <row r="13" spans="1:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="98" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="67"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+    </row>
+    <row r="14" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
+      <c r="R14" s="91"/>
+      <c r="S14" s="91"/>
+      <c r="T14" s="55"/>
+    </row>
+    <row r="15" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="66"/>
-      <c r="M13" s="66"/>
-      <c r="N13" s="66"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
-    </row>
-    <row r="14" spans="1:20" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="92" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="92" t="s">
-        <v>6</v>
-      </c>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="93"/>
-      <c r="N14" s="93"/>
-      <c r="O14" s="93"/>
-      <c r="P14" s="93"/>
-      <c r="Q14" s="93"/>
-      <c r="R14" s="93"/>
-      <c r="S14" s="93"/>
-      <c r="T14" s="54"/>
-    </row>
-    <row r="15" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="89" t="s">
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="57" t="s">
+      <c r="G15" s="96" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="91" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="90"/>
-      <c r="T15" s="56"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="89"/>
+      <c r="Q15" s="89"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="89"/>
+      <c r="T15" s="57"/>
     </row>
     <row r="16" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="60" t="s">
         <v>117</v>
-      </c>
-      <c r="B16" s="60" t="s">
-        <v>118</v>
       </c>
       <c r="C16" s="61"/>
       <c r="D16" s="61"/>
       <c r="E16" s="61"/>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="62" t="s">
-        <v>119</v>
+      <c r="G16" s="70" t="s">
+        <v>118</v>
       </c>
       <c r="H16" s="61"/>
       <c r="I16" s="61"/>
@@ -3482,50 +3485,50 @@
       <c r="T16" s="26"/>
     </row>
     <row r="17" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="89" t="s">
+      <c r="A17" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="88" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="90"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="91" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="90"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="90"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="56"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="57"/>
     </row>
     <row r="18" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C18" s="61"/>
       <c r="D18" s="61"/>
       <c r="E18" s="61"/>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="62" t="s">
-        <v>123</v>
+      <c r="G18" s="70" t="s">
+        <v>122</v>
       </c>
       <c r="H18" s="61"/>
       <c r="I18" s="61"/>
@@ -3542,50 +3545,50 @@
       <c r="T18" s="26"/>
     </row>
     <row r="19" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="89" t="s">
+      <c r="A19" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="88" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="96" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="91" t="s">
-        <v>125</v>
-      </c>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="90"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="90"/>
-      <c r="R19" s="90"/>
-      <c r="S19" s="90"/>
-      <c r="T19" s="56"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="89"/>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="89"/>
+      <c r="N19" s="89"/>
+      <c r="O19" s="89"/>
+      <c r="P19" s="89"/>
+      <c r="Q19" s="89"/>
+      <c r="R19" s="89"/>
+      <c r="S19" s="89"/>
+      <c r="T19" s="57"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="60" t="s">
         <v>126</v>
-      </c>
-      <c r="B20" s="60" t="s">
-        <v>127</v>
       </c>
       <c r="C20" s="61"/>
       <c r="D20" s="61"/>
       <c r="E20" s="61"/>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="62" t="s">
-        <v>128</v>
+      <c r="G20" s="70" t="s">
+        <v>127</v>
       </c>
       <c r="H20" s="61"/>
       <c r="I20" s="61"/>
@@ -3602,50 +3605,50 @@
       <c r="T20" s="26"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="B21" s="89" t="s">
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="96" t="s">
         <v>130</v>
       </c>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="91" t="s">
-        <v>131</v>
-      </c>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="90"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-      <c r="O21" s="90"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="90"/>
-      <c r="R21" s="90"/>
-      <c r="S21" s="90"/>
-      <c r="T21" s="56"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="89"/>
+      <c r="N21" s="89"/>
+      <c r="O21" s="89"/>
+      <c r="P21" s="89"/>
+      <c r="Q21" s="89"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="89"/>
+      <c r="T21" s="57"/>
     </row>
     <row r="22" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C22" s="61"/>
       <c r="D22" s="61"/>
       <c r="E22" s="61"/>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="62" t="s">
-        <v>133</v>
+      <c r="G22" s="70" t="s">
+        <v>132</v>
       </c>
       <c r="H22" s="61"/>
       <c r="I22" s="61"/>
@@ -3662,49 +3665,49 @@
       <c r="T22" s="26"/>
     </row>
     <row r="23" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="B23" s="89" t="s">
+      <c r="A23" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="88" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="96" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="90"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="91" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="90"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="90"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="90"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="90"/>
-      <c r="R23" s="90"/>
-      <c r="S23" s="90"/>
-      <c r="T23" s="56"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="89"/>
+      <c r="P23" s="89"/>
+      <c r="Q23" s="89"/>
+      <c r="R23" s="89"/>
+      <c r="S23" s="89"/>
+      <c r="T23" s="57"/>
     </row>
     <row r="24" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24" s="60" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C24" s="61"/>
       <c r="D24" s="61"/>
       <c r="E24" s="61"/>
-      <c r="F24" s="58" t="s">
+      <c r="F24" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="62" t="s">
+      <c r="G24" s="70" t="s">
         <v>90</v>
       </c>
       <c r="H24" s="61"/>
@@ -3722,50 +3725,50 @@
       <c r="T24" s="26"/>
     </row>
     <row r="25" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="89" t="s">
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="96" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="90"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="91" t="s">
-        <v>139</v>
-      </c>
-      <c r="H25" s="90"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="90"/>
-      <c r="K25" s="90"/>
-      <c r="L25" s="90"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="90"/>
-      <c r="O25" s="90"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="90"/>
-      <c r="R25" s="90"/>
-      <c r="S25" s="90"/>
-      <c r="T25" s="56"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="89"/>
+      <c r="O25" s="89"/>
+      <c r="P25" s="89"/>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="89"/>
+      <c r="T25" s="57"/>
     </row>
     <row r="26" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="60" t="s">
         <v>140</v>
-      </c>
-      <c r="B26" s="60" t="s">
-        <v>141</v>
       </c>
       <c r="C26" s="61"/>
       <c r="D26" s="61"/>
       <c r="E26" s="61"/>
-      <c r="F26" s="58" t="s">
+      <c r="F26" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="62" t="s">
-        <v>142</v>
+      <c r="G26" s="70" t="s">
+        <v>141</v>
       </c>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -3782,67 +3785,67 @@
       <c r="T26" s="26"/>
     </row>
     <row r="27" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="75" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="66"/>
+      <c r="A27" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G26:S26"/>
+    <mergeCell ref="G18:S18"/>
+    <mergeCell ref="G15:S15"/>
+    <mergeCell ref="G25:S25"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A27:T27"/>
+    <mergeCell ref="G16:S16"/>
+    <mergeCell ref="A11:T11"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A13:T13"/>
+    <mergeCell ref="G24:S24"/>
     <mergeCell ref="G14:S14"/>
+    <mergeCell ref="G19:S19"/>
+    <mergeCell ref="G20:S20"/>
+    <mergeCell ref="G22:S22"/>
+    <mergeCell ref="G21:S21"/>
+    <mergeCell ref="G17:S17"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
     <mergeCell ref="P6:R6"/>
-    <mergeCell ref="A11:T11"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G23:S23"/>
     <mergeCell ref="A5:T5"/>
     <mergeCell ref="M6:O6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="G15:S15"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B19:E19"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="G23:S23"/>
-    <mergeCell ref="G16:S16"/>
-    <mergeCell ref="A27:T27"/>
-    <mergeCell ref="G18:S18"/>
-    <mergeCell ref="G26:S26"/>
-    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A13:T13"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="G22:S22"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="G21:S21"/>
-    <mergeCell ref="G19:S19"/>
-    <mergeCell ref="G17:S17"/>
-    <mergeCell ref="G25:S25"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="G24:S24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="G20:S20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
